--- a/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260702.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260702.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D54"/>
+  <dimension ref="A1:D53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>156,755</t>
+          <t>157,255</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>26.35%</t>
+          <t>26.15%</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>17,935</t>
+          <t>18,035</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>9.28%</t>
+          <t>9.26%</t>
         </is>
       </c>
     </row>
@@ -655,12 +655,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>113,700</t>
+          <t>114,000</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>7.39%</t>
+          <t>7.38%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>57,995</t>
+          <t>58,195</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.20%</t>
+          <t>6.59%</t>
         </is>
       </c>
     </row>
@@ -699,78 +699,78 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>138,065</t>
+          <t>138,465</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.44%</t>
+          <t>5.64%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>NOW US</t>
+          <t>SO US</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>ServiceNow Inc</t>
+          <t>南方公司</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>67,610</t>
+          <t>74,675</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.26%</t>
+          <t>3.38%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>SO US</t>
+          <t>NOW US</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>南方公司</t>
+          <t>ServiceNow Inc</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>74,475</t>
+          <t>68,110</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.23%</t>
+          <t>3.34%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>EQIX US</t>
+          <t>C_NTD</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Equinix公司</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>6,525</t>
+          <t>213,019,080</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.02%</t>
+          <t>3.08%</t>
         </is>
       </c>
     </row>
@@ -787,100 +787,100 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>51,365</t>
+          <t>51,465</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.95%</t>
+          <t>3.08%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>CEG US</t>
+          <t>EQIX US</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>星座能源公司</t>
+          <t>Equinix公司</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>22,475</t>
+          <t>6,525</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.42%</t>
+          <t>3.02%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>NET US</t>
+          <t>CEG US</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Cloudflare公司</t>
+          <t>星座能源公司</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>20,793</t>
+          <t>22,575</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.34%</t>
+          <t>2.49%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>AEP US</t>
+          <t>NET US</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>美國電力公司</t>
+          <t>Cloudflare公司</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>35,860</t>
+          <t>20,893</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.21%</t>
+          <t>2.34%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>DLR US</t>
+          <t>AEP US</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>數位不動產信託公司</t>
+          <t>美國電力公司</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>23,115</t>
+          <t>35,960</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>1.86%</t>
+          <t>2.30%</t>
         </is>
       </c>
     </row>
@@ -897,78 +897,78 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>58,065</t>
+          <t>58,265</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>1.80%</t>
+          <t>1.88%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>ALAB US</t>
+          <t>DLR US</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Astera實驗室公司</t>
+          <t>數位不動產信託公司</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>9,090</t>
+          <t>23,215</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.79%</t>
+          <t>1.86%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>HPE US</t>
+          <t>ALAB US</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>慧與</t>
+          <t>Astera實驗室公司</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>87,555</t>
+          <t>9,190</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.76%</t>
+          <t>1.72%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>C_USD</t>
+          <t>HPE US</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>慧與</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>3,701,902</t>
+          <t>87,855</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.69%</t>
+          <t>1.67%</t>
         </is>
       </c>
     </row>
@@ -985,56 +985,56 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>30,228</t>
+          <t>30,328</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.56%</t>
+          <t>1.61%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>VST US</t>
+          <t>XEL US</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>維斯達能源公司</t>
+          <t>Xcel 能源</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>22,180</t>
+          <t>41,210</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.55%</t>
+          <t>1.56%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>XEL US</t>
+          <t>VST US</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Xcel 能源</t>
+          <t>維斯達能源公司</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>41,210</t>
+          <t>22,280</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.50%</t>
+          <t>1.55%</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.43%</t>
+          <t>1.49%</t>
         </is>
       </c>
     </row>
@@ -1078,29 +1078,29 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.40%</t>
+          <t>1.33%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>C_NTD</t>
+          <t>ED US</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>聯合愛迪生</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>95,286,823</t>
+          <t>24,278</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.36%</t>
+          <t>1.28%</t>
         </is>
       </c>
     </row>
@@ -1122,190 +1122,190 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.22%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>ED US</t>
+          <t>WEC US</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>聯合愛迪生</t>
+          <t>WEC能源集團公司</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>24,278</t>
+          <t>21,045</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.23%</t>
+          <t>1.15%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>WEC US</t>
+          <t>PCG US</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>WEC能源集團公司</t>
+          <t>太平洋電力瓦斯公司</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>21,045</t>
+          <t>144,355</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.12%</t>
+          <t>1.14%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>PCG US</t>
+          <t>AEE US</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>太平洋電力瓦斯公司</t>
+          <t>阿莫林公司</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>144,355</t>
+          <t>18,201</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.09%</t>
+          <t>0.97%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>AEE US</t>
+          <t>CNP US</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>阿莫林公司</t>
+          <t>Centerpoint能源</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>18,201</t>
+          <t>42,760</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>0.88%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>CRWV US</t>
+          <t>NRG US</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>CoreWeave Inc</t>
+          <t>NRG Energy Inc</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>22,447</t>
+          <t>13,405</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.88%</t>
+          <t>0.85%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>NRG US</t>
+          <t>CRWV US</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>NRG Energy Inc</t>
+          <t>CoreWeave Inc</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>13,405</t>
+          <t>22,547</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>0.85%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>CNP US</t>
+          <t>PPL US</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Centerpoint能源</t>
+          <t>PPL Corp</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>42,760</t>
+          <t>49,190</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>0.84%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>PPL US</t>
+          <t>C_USD</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>PPL Corp</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>49,190</t>
+          <t>1,639,023</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.80%</t>
+          <t>0.76%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>RDI_NTD</t>
+          <t>RDI_USD</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -1315,32 +1315,10 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>111,499,250</t>
+          <t>-682,107</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>RDI_USD</t>
-        </is>
-      </c>
-      <c r="B54" s="3" t="inlineStr">
-        <is>
-          <t>RECEIVABLES FOR DISPOSAL OF INVESTMENTS</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="inlineStr">
-        <is>
-          <t>1,437,121</t>
-        </is>
-      </c>
-      <c r="D54" s="4" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
